--- a/www/download/IND.value.m.mv.rpO1.xlsx
+++ b/www/download/IND.value.m.mv.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>833.007</t>
+          <t>833006501.116931</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>745.787</t>
+          <t>745786818.52123</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>781.124</t>
+          <t>781123896.18257</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>878.487</t>
+          <t>878486887.357163</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>925.658</t>
+          <t>925658198.737621</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1071.013</t>
+          <t>1071013035.9407</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1121.055</t>
+          <t>1121054885.72026</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1099.535</t>
+          <t>1099535210.95153</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1021.754</t>
+          <t>1021753979.75878</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>863.409</t>
+          <t>863408644.617785</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>781.63</t>
+          <t>781630412.519616</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>690.872</t>
+          <t>690872488.934875</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>518.719</t>
+          <t>518719025.722322</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>391.48</t>
+          <t>391480392.066809</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>381.713</t>
+          <t>381713173.846944</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1118.584</t>
+          <t>1118584306.55855</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>995.415</t>
+          <t>995415067.346593</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1028.72</t>
+          <t>1028719592.67296</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1155.691</t>
+          <t>1155690537.80343</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1237.322</t>
+          <t>1237322495.01166</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1383.042</t>
+          <t>1383042363.85428</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1451.525</t>
+          <t>1451524841.64918</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1374.48</t>
+          <t>1374479921.8131</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1318.274</t>
+          <t>1318273601.92961</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1070.374</t>
+          <t>1070373935.64808</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>948.25</t>
+          <t>948249917.283216</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>796.084</t>
+          <t>796083566.865969</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>579.229</t>
+          <t>579228833.738631</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>394.906</t>
+          <t>394905765.622486</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>408.98</t>
+          <t>408980396.237578</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>862.579</t>
+          <t>862578800.768201</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>782.298</t>
+          <t>782298130.990046</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>796.468</t>
+          <t>796468288.753091</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>887.373</t>
+          <t>887373203.301103</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>963.003</t>
+          <t>963002601.5272</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1069.217</t>
+          <t>1069216591.96894</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1158.449</t>
+          <t>1158448597.96424</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1126.152</t>
+          <t>1126152417.03623</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1066.416</t>
+          <t>1066415542.38309</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>873.719</t>
+          <t>873719063.453034</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>778.006</t>
+          <t>778005712.494504</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>654.355</t>
+          <t>654355470.349172</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>486.638</t>
+          <t>486637627.918596</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>367.007</t>
+          <t>367007276.771334</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>381.936</t>
+          <t>381936309.789858</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1090.969</t>
+          <t>1090969314.44526</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>909.243</t>
+          <t>909243222.286337</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>950.895</t>
+          <t>950895435.841977</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1097.156</t>
+          <t>1097156131.77722</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1124.985</t>
+          <t>1124985073.86102</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1180.109</t>
+          <t>1180109162.37682</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1265.558</t>
+          <t>1265557503.47193</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1206.329</t>
+          <t>1206328506.87393</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1098.223</t>
+          <t>1098222642.73343</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>883.876</t>
+          <t>883876484.44477</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>775.046</t>
+          <t>775045801.965129</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>670.69</t>
+          <t>670690225.067299</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>504.029</t>
+          <t>504028532.435667</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>393.846</t>
+          <t>393846095.547761</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>387.264</t>
+          <t>387263581.494448</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>759.541</t>
+          <t>759540633.083698</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>702.913</t>
+          <t>702912780.638657</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>711.161</t>
+          <t>711161434.107904</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>811.4</t>
+          <t>811400157.093242</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>845.114</t>
+          <t>845114008.026763</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>966.102</t>
+          <t>966101650.157224</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1031.989</t>
+          <t>1031988526.79857</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>960.95</t>
+          <t>960950189.405773</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>901.534</t>
+          <t>901534352.871002</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>752.036</t>
+          <t>752035503.461284</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>696.047</t>
+          <t>696046777.749608</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>603.906</t>
+          <t>603906365.198655</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>529.489</t>
+          <t>529489214.704007</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>397.556</t>
+          <t>397555532.911707</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>411.692</t>
+          <t>411692319.575089</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>867.612</t>
+          <t>867612123.9141</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>770.977</t>
+          <t>770977215.842898</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>793.992</t>
+          <t>793991885.643629</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>910.991</t>
+          <t>910990964.561419</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>974.045</t>
+          <t>974044955.781085</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1073.089</t>
+          <t>1073089486.9398</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1153.774</t>
+          <t>1153773736.384</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1112.169</t>
+          <t>1112169307.80065</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1051.921</t>
+          <t>1051921472.92698</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>875.345</t>
+          <t>875345041.853511</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>784.502</t>
+          <t>784502438.562183</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>680.371</t>
+          <t>680371295.09669</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>510.752</t>
+          <t>510752037.836062</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>390.845</t>
+          <t>390844910.052131</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>386.147</t>
+          <t>386146506.872972</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>885.332</t>
+          <t>885331531.380151</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>797.923</t>
+          <t>797923417.278755</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>827.861</t>
+          <t>827861481.2629</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>917.18</t>
+          <t>917179688.102799</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>978.274</t>
+          <t>978273671.970305</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1104.971</t>
+          <t>1104971129.59467</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1163.265</t>
+          <t>1163265391.97101</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1097.958</t>
+          <t>1097958296.99204</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1030.903</t>
+          <t>1030903063.75945</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>855.701</t>
+          <t>855701218.187996</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>747.588</t>
+          <t>747588312.682349</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>627.675</t>
+          <t>627674855.315434</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>451.63</t>
+          <t>451629587.082062</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>337.777</t>
+          <t>337776716.308995</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>322.91</t>
+          <t>322909615.268777</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1012.279</t>
+          <t>1012278661.8147</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>917.311</t>
+          <t>917311089.220526</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>953.095</t>
+          <t>953095370.347778</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1048.653</t>
+          <t>1048652658.35322</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1127.173</t>
+          <t>1127172736.67091</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1265.836</t>
+          <t>1265835823.15372</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1316.653</t>
+          <t>1316653381.37629</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1284.338</t>
+          <t>1284338457.11879</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1239.22</t>
+          <t>1239220308.8392</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1061.664</t>
+          <t>1061664003.90299</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>910.107</t>
+          <t>910107474.563246</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>797.912</t>
+          <t>797912035.488227</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>584.469</t>
+          <t>584469037.932671</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>455.075</t>
+          <t>455074556.66012</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>418.715</t>
+          <t>418715444.846846</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>778.179</t>
+          <t>778178913.587715</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>840.868</t>
+          <t>840868222.557064</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>878.164</t>
+          <t>878163514.981302</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>999.19</t>
+          <t>999189668.965845</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1068.795</t>
+          <t>1068795375.01941</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1173.069</t>
+          <t>1173068894.59376</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1267.544</t>
+          <t>1267543546.40385</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1232.487</t>
+          <t>1232486646.94108</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1159.626</t>
+          <t>1159625834.0452</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>913.005</t>
+          <t>913004883.96438</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>820.218</t>
+          <t>820218489.636246</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>688.724</t>
+          <t>688723977.310146</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>498999707.086913</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>337.477</t>
+          <t>337476733.392507</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>332.47</t>
+          <t>332470268.364037</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1009.929</t>
+          <t>1009929267.98184</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>913.869</t>
+          <t>913868989.819343</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>930.288</t>
+          <t>930288100.678485</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1034.173</t>
+          <t>1034173026.32117</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1106.216</t>
+          <t>1106216212.10733</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1277.253</t>
+          <t>1277253034.29196</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1354.343</t>
+          <t>1354342934.48506</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1305.314</t>
+          <t>1305313652.67091</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1226.122</t>
+          <t>1226122350.99768</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>992.871</t>
+          <t>992870801.844902</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>875.405</t>
+          <t>875404897.031259</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>724.622</t>
+          <t>724622278.615596</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>524.72</t>
+          <t>524719663.167355</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>358.539</t>
+          <t>358538712.233487</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>373.7</t>
+          <t>373700450.0506</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>884.516</t>
+          <t>884515629.893134</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>783.752</t>
+          <t>783752006.527987</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>805.305</t>
+          <t>805304815.308581</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>921.611</t>
+          <t>921610569.875387</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>981.506</t>
+          <t>981506093.133454</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1084.853</t>
+          <t>1084853079.98273</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1171.578</t>
+          <t>1171577879.55543</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1126.504</t>
+          <t>1126504118.06616</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1084.442</t>
+          <t>1084442073.9006</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>896.435</t>
+          <t>896435107.250916</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>788.01</t>
+          <t>788010343.318093</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>666.317</t>
+          <t>666316996.81981</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>499.737</t>
+          <t>499736640.646595</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>357.631</t>
+          <t>357630534.302483</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>373.865</t>
+          <t>373864895.65673</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>901.227</t>
+          <t>901226514.903347</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>811.722</t>
+          <t>811721954.005074</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>850.041</t>
+          <t>850040559.284442</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>943.521</t>
+          <t>943520955.101655</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1017.781</t>
+          <t>1017780836.39428</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1144.26</t>
+          <t>1144260195.16831</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1206.384</t>
+          <t>1206384025.26499</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1148.177</t>
+          <t>1148177354.08194</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1088.966</t>
+          <t>1088966196.64118</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>901.026</t>
+          <t>901025543.124642</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>800.904</t>
+          <t>800904266.730214</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>682.053</t>
+          <t>682053492.042155</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>511.18</t>
+          <t>511180336.474245</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>356.29</t>
+          <t>356289586.592291</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>341.924</t>
+          <t>341924443.671457</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>943.815</t>
+          <t>943814885.506278</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>841.981</t>
+          <t>841980809.873672</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>837.463</t>
+          <t>837462817.475867</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>929.329</t>
+          <t>929329321.307679</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>987.695</t>
+          <t>987694964.779494</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1133.236</t>
+          <t>1133236026.11205</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1184.101</t>
+          <t>1184101005.65459</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1096.209</t>
+          <t>1096208672.27332</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1044.93</t>
+          <t>1044929859.48479</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>888.473</t>
+          <t>888472668.188363</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>775.249</t>
+          <t>775248556.146595</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>646.041</t>
+          <t>646041437.155078</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>497.246</t>
+          <t>497246487.036949</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>393.429</t>
+          <t>393429472.27593</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>399.124</t>
+          <t>399123540.172667</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>975.884</t>
+          <t>975884019.235112</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>867.635</t>
+          <t>867635186.559877</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>877.264</t>
+          <t>877264181.96042</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>976.131</t>
+          <t>976130987.647325</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1073.69</t>
+          <t>1073689862.12816</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1201.638</t>
+          <t>1201638282.01849</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1294.499</t>
+          <t>1294498545.82388</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1234.675</t>
+          <t>1234675138.66513</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1183.397</t>
+          <t>1183396534.33153</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>973.876</t>
+          <t>973875502.408221</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>869.274</t>
+          <t>869273916.015552</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>733.956</t>
+          <t>733955898.923442</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>528.227</t>
+          <t>528227310.53239</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>368.492</t>
+          <t>368492330.736582</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>388.893</t>
+          <t>388893067.615407</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>880.164</t>
+          <t>880163912.270545</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>808.658</t>
+          <t>808658357.363415</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>831.834</t>
+          <t>831834192.110751</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>908.218</t>
+          <t>908217588.088886</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>980.459</t>
+          <t>980459298.533565</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1108.564</t>
+          <t>1108563699.16116</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1175.114</t>
+          <t>1175114268.38386</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1136.702</t>
+          <t>1136702032.36965</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1084.608</t>
+          <t>1084607971.15956</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>900.474</t>
+          <t>900473546.331524</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>805.627</t>
+          <t>805626741.170855</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>684.117</t>
+          <t>684116893.904034</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>506.771</t>
+          <t>506770613.010677</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>358.759</t>
+          <t>358759119.395302</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>353.935</t>
+          <t>353935418.683947</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>927.979</t>
+          <t>927978540.449774</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>814.457</t>
+          <t>814457234.299711</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>845.996</t>
+          <t>845996464.58717</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>976.538</t>
+          <t>976537874.664369</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1064.162</t>
+          <t>1064162347.34642</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1208.881</t>
+          <t>1208881042.86511</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1296.362</t>
+          <t>1296362387.00332</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1245.406</t>
+          <t>1245406450.65341</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1178.891</t>
+          <t>1178891179.76918</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>978.453</t>
+          <t>978453402.459873</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>889.765</t>
+          <t>889764778.013889</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>762.661</t>
+          <t>762660657.027313</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>572.038</t>
+          <t>572037548.001835</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>410.156</t>
+          <t>410155851.612738</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>428.085</t>
+          <t>428084506.950752</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>892.52</t>
+          <t>892520469.729399</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>825.735</t>
+          <t>825734541.964442</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>902.178</t>
+          <t>902177548.887235</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>995.521</t>
+          <t>995521450.931736</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1101.745</t>
+          <t>1101745065.17386</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1248.734</t>
+          <t>1248733606.08113</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1277.348</t>
+          <t>1277348182.19926</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1295.428</t>
+          <t>1295428442.43384</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1216.747</t>
+          <t>1216746693.87851</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1005.327</t>
+          <t>1005326735.71343</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>896.166</t>
+          <t>896165685.114916</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>776.514</t>
+          <t>776514132.313762</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>577.871</t>
+          <t>577871163.13863</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>429.046</t>
+          <t>429045854.379646</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>441.004</t>
+          <t>441004197.144756</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1087.098</t>
+          <t>1087098282.6877</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>946.847</t>
+          <t>946847059.038448</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>964.118</t>
+          <t>964118372.43496</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1044.722</t>
+          <t>1044722154.95497</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1119.654</t>
+          <t>1119653535.75412</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1275.961</t>
+          <t>1275961007.39201</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1308.962</t>
+          <t>1308961573.06298</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1249.679</t>
+          <t>1249679226.88214</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1180.469</t>
+          <t>1180469335.88555</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>967.297</t>
+          <t>967297272.582128</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>863.648</t>
+          <t>863648020.137043</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>708.379</t>
+          <t>708378981.039004</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>520.184</t>
+          <t>520183650.925933</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>343.563</t>
+          <t>343562593.744234</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>331.94</t>
+          <t>331940409.691571</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>731.714</t>
+          <t>731713629.688235</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>659.282</t>
+          <t>659281752.263877</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>690.732</t>
+          <t>690731784.944016</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>816.673</t>
+          <t>816672683.14036</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>857.245</t>
+          <t>857245300.830563</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>985.991</t>
+          <t>985991111.255515</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1034.061</t>
+          <t>1034061244.87534</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>987.074</t>
+          <t>987073525.351502</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>933.258</t>
+          <t>933257794.915714</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>802.163</t>
+          <t>802163148.118828</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>712.156</t>
+          <t>712155986.663165</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>609.954</t>
+          <t>609953935.298832</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>453.761</t>
+          <t>453761112.874015</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>352.397</t>
+          <t>352396649.231132</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>336.967</t>
+          <t>336967111.000578</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>796.243</t>
+          <t>796242967.733712</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>676.271</t>
+          <t>676271107.133819</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>728.827</t>
+          <t>728826958.618166</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>806.726</t>
+          <t>806725623.233051</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>873.805</t>
+          <t>873805326.614818</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1036.843</t>
+          <t>1036842596.95928</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1118.571</t>
+          <t>1118570543.96736</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1038.803</t>
+          <t>1038803354.75322</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>973.527</t>
+          <t>973527213.904382</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>788.609</t>
+          <t>788608554.012113</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>713.052</t>
+          <t>713052137.292196</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>620.937</t>
+          <t>620936695.262146</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>464.237</t>
+          <t>464237431.418217</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>351.366</t>
+          <t>351366438.695082</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>342.816</t>
+          <t>342816286.070996</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>933.501</t>
+          <t>933500968.664924</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>828.84</t>
+          <t>828839569.942</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>826.998</t>
+          <t>826998163.756331</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>936.529</t>
+          <t>936529093.538527</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1044.746</t>
+          <t>1044745657.67638</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1139.515</t>
+          <t>1139515094.55282</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1221.646</t>
+          <t>1221646270.37194</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1143.662</t>
+          <t>1143661566.45582</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1076.433</t>
+          <t>1076433052.15098</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>897.118</t>
+          <t>897117906.492823</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>790.287</t>
+          <t>790287207.812096</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>668.699</t>
+          <t>668698845.303811</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>507.206</t>
+          <t>507206160.698862</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>423.325</t>
+          <t>423325409.617353</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>429.54</t>
+          <t>429539583.954034</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>932.065</t>
+          <t>932065475.104203</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>841.244</t>
+          <t>841244402.892298</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>877.621</t>
+          <t>877621106.140299</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>950.342</t>
+          <t>950341961.718959</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1026.423</t>
+          <t>1026423193.9434</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1140.436</t>
+          <t>1140435669.13182</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1213.898</t>
+          <t>1213897836.50668</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1186.575</t>
+          <t>1186575317.94338</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1143.912</t>
+          <t>1143912015.33876</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>946.314</t>
+          <t>946314078.038907</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>853.648</t>
+          <t>853648253.879736</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>735.1</t>
+          <t>735100187.762316</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>546.617</t>
+          <t>546617434.796209</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>373.363</t>
+          <t>373362758.618197</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>378.887</t>
+          <t>378886827.218377</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>905.153</t>
+          <t>905153072.550384</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>815.441</t>
+          <t>815441165.912813</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>847.282</t>
+          <t>847282113.624499</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>965.665</t>
+          <t>965664772.11224</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1077.634</t>
+          <t>1077634423.32925</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1241.736</t>
+          <t>1241735628.80122</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1348.205</t>
+          <t>1348204660.35818</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1296.015</t>
+          <t>1296014885.51726</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1216.639</t>
+          <t>1216638828.75725</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1010.486</t>
+          <t>1010485883.21648</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>899.289</t>
+          <t>899289434.459752</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>779.624</t>
+          <t>779624386.335954</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>582.269</t>
+          <t>582268803.131489</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>443.565</t>
+          <t>443564604.995324</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>443.458</t>
+          <t>443457805.244694</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1127.398</t>
+          <t>1127397886.25902</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1049.835</t>
+          <t>1049834527.38652</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1068.359</t>
+          <t>1068358578.64276</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1174.662</t>
+          <t>1174661519.13458</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1210.657</t>
+          <t>1210657134.96729</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1407.2</t>
+          <t>1407199572.8535</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1543.047</t>
+          <t>1543047351.98258</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1480.086</t>
+          <t>1480086101.59458</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1426.772</t>
+          <t>1426772025.80542</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1156.414</t>
+          <t>1156414162.79501</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1056.749</t>
+          <t>1056748728.17188</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>902.779</t>
+          <t>902778520.952207</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>659.443</t>
+          <t>659442587.189248</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>482.767</t>
+          <t>482767393.228675</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>478.323</t>
+          <t>478323488.681883</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>859.796</t>
+          <t>859796356.855951</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>797.801</t>
+          <t>797801279.494571</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>870.379</t>
+          <t>870378994.90235</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>969.995</t>
+          <t>969994727.037072</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1077.461</t>
+          <t>1077460948.29966</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1173.5</t>
+          <t>1173499595.39116</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1260.654</t>
+          <t>1260653884.13767</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1178.193</t>
+          <t>1178193274.50974</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1138.08</t>
+          <t>1138080256.2734</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>947.633</t>
+          <t>947633422.660694</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>851.268</t>
+          <t>851268058.934711</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>724.341</t>
+          <t>724341208.246123</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>533.52</t>
+          <t>533519641.259081</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>401.064</t>
+          <t>401064152.171857</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>408.008</t>
+          <t>408007721.967047</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>860.19</t>
+          <t>860190071.000804</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>769.666</t>
+          <t>769665932.995062</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>786.368</t>
+          <t>786367992.389787</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>867.598</t>
+          <t>867597896.17091</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>941.213</t>
+          <t>941212518.556589</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1066.162</t>
+          <t>1066161745.8532</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1164.667</t>
+          <t>1164666527.58688</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1107.976</t>
+          <t>1107976424.61687</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1079.168</t>
+          <t>1079167710.70052</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>867.55</t>
+          <t>867550135.191634</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>791.761</t>
+          <t>791761027.558413</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>651.221</t>
+          <t>651221350.301361</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>482.007</t>
+          <t>482006586.592373</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>367.262</t>
+          <t>367261555.768002</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>423.096</t>
+          <t>423095662.29256</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>954.03</t>
+          <t>954029551.66922</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>867.491</t>
+          <t>867490596.399121</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>900.528</t>
+          <t>900527610.402965</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>987.386</t>
+          <t>987386361.785931</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1066.011</t>
+          <t>1066010619.67542</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1147.27</t>
+          <t>1147270385.76982</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1139.812</t>
+          <t>1139812427.49859</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1200.243</t>
+          <t>1200243206.64582</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1044.445</t>
+          <t>1044445017.01506</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>847.405</t>
+          <t>847405336.519449</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>791.089</t>
+          <t>791089430.478601</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>685.198</t>
+          <t>685197889.8145</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>524.078</t>
+          <t>524078064.252873</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>418.646</t>
+          <t>418645921.731409</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>376.619</t>
+          <t>376619040.304294</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>667.413</t>
+          <t>667413373.398835</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>574.616</t>
+          <t>574616366.790351</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>598.264</t>
+          <t>598264297.31958</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>711.051</t>
+          <t>711050512.464793</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>791.408</t>
+          <t>791407503.625326</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>931.112</t>
+          <t>931112033.768443</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1036.053</t>
+          <t>1036053148.13144</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>970.653</t>
+          <t>970653196.772536</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>904.244</t>
+          <t>904243926.113136</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>718.391</t>
+          <t>718391320.588714</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>635.969</t>
+          <t>635968580.743038</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>522.875</t>
+          <t>522875488.378591</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>383.938</t>
+          <t>383938181.831382</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>286.802</t>
+          <t>286802399.488606</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>282.95</t>
+          <t>282949783.158772</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1022.584</t>
+          <t>1022584390.00666</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>957.378</t>
+          <t>957377919.201873</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>964.175</t>
+          <t>964174764.607173</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1088.244</t>
+          <t>1088243568.29701</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1215.068</t>
+          <t>1215067511.82915</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1363.707</t>
+          <t>1363707286.64763</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1354.561</t>
+          <t>1354560539.99714</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1332.92</t>
+          <t>1332920195.39522</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1277.509</t>
+          <t>1277509145.28072</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1055.986</t>
+          <t>1055986198.20119</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>873.412</t>
+          <t>873412172.716069</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>794.56</t>
+          <t>794560423.87922</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>586.589</t>
+          <t>586588939.534849</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>502.418</t>
+          <t>502418278.061527</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>507.429</t>
+          <t>507428540.433449</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>844.339</t>
+          <t>844339118.21027</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>754.02</t>
+          <t>754019533.646412</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>772.986</t>
+          <t>772986090.705324</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>854.721</t>
+          <t>854721360.805652</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>927.32</t>
+          <t>927320449.275941</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1044.996</t>
+          <t>1044995963.63759</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1117.42</t>
+          <t>1117420063.62696</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1091.944</t>
+          <t>1091944251.33719</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1044.176</t>
+          <t>1044176054.37706</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>870.467</t>
+          <t>870466840.33523</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>756.86</t>
+          <t>756859954.875281</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>638.533</t>
+          <t>638533468.744298</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>469.551</t>
+          <t>469550918.208936</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>339.696</t>
+          <t>339695949.644624</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>346.91</t>
+          <t>346910300.994081</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1347.041</t>
+          <t>1347041346.36765</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1236.987</t>
+          <t>1236987201.8533</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1320.885</t>
+          <t>1320885421.08745</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1559.383</t>
+          <t>1559383402.97991</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1734.745</t>
+          <t>1734744780.81617</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1608.781</t>
+          <t>1608780662.00374</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1569.171</t>
+          <t>1569171163.33339</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1419.286</t>
+          <t>1419286420.0282</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1302.107</t>
+          <t>1302106755.27855</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>995.482</t>
+          <t>995482423.054483</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>887.437</t>
+          <t>887437344.208594</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>728.505</t>
+          <t>728505196.527313</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>534.637</t>
+          <t>534636707.742745</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>382.856</t>
+          <t>382856071.543584</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>371.344</t>
+          <t>371343522.94721</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>893.955</t>
+          <t>893954870.152458</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>815.678</t>
+          <t>815677799.826729</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>853.597</t>
+          <t>853597386.411894</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>951.491</t>
+          <t>951491007.869351</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1050.2</t>
+          <t>1050199864.58904</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1208.674</t>
+          <t>1208674263.26186</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1297.184</t>
+          <t>1297183558.02138</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1253.257</t>
+          <t>1253257286.40123</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1196.784</t>
+          <t>1196784068.98759</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>988.265</t>
+          <t>988265068.051865</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>896.488</t>
+          <t>896488417.934127</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>745.859</t>
+          <t>745859283.936149</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>550.401</t>
+          <t>550400838.744973</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>420.985</t>
+          <t>420985265.271967</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>380.9</t>
+          <t>380899684.904125</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1051.518</t>
+          <t>1051517866.09971</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>948.273</t>
+          <t>948273328.650025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>889.237</t>
+          <t>889236726.522038</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1194.029</t>
+          <t>1194029298.21385</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1127.237</t>
+          <t>1127237150.57635</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1399.944</t>
+          <t>1399943621.71825</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1617.343</t>
+          <t>1617343289.08678</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1538.714</t>
+          <t>1538714341.21314</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1451.233</t>
+          <t>1451233242.16412</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1010.781</t>
+          <t>1010780961.64982</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1035.014</t>
+          <t>1035013857.04393</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>883.423</t>
+          <t>883422714.868338</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>658.036</t>
+          <t>658035986.259918</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>515.109</t>
+          <t>515108652.889838</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>478.443</t>
+          <t>478443160.947334</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>898.657</t>
+          <t>898657310.937232</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>799.504</t>
+          <t>799503894.164987</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>833.218</t>
+          <t>833217816.192923</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>948.656</t>
+          <t>948655543.874739</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1002.908</t>
+          <t>1002907931.22254</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1134.534</t>
+          <t>1134533875.91946</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1181.769</t>
+          <t>1181769499.13663</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1220.859</t>
+          <t>1220859253.41684</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1137.129</t>
+          <t>1137128825.13781</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>906.733</t>
+          <t>906733387.97569</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>809.908</t>
+          <t>809908125.429357</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>683.595</t>
+          <t>683594978.564925</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>499.356</t>
+          <t>499355971.073695</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>370.527</t>
+          <t>370527025.561929</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>363.729</t>
+          <t>363728597.230971</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>713.117</t>
+          <t>713117256.916907</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>664.869</t>
+          <t>664868791.716286</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>704.025</t>
+          <t>704024773.840944</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>791.156</t>
+          <t>791155533.10815</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>837.843</t>
+          <t>837842779.434214</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>925.571</t>
+          <t>925571170.346727</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1021.037</t>
+          <t>1021037468.83211</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>958.789</t>
+          <t>958788907.771502</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>921.859</t>
+          <t>921859114.552059</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>762.275</t>
+          <t>762274695.738084</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>673.161</t>
+          <t>673160724.902436</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>567.884</t>
+          <t>567883548.492827</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>411.221</t>
+          <t>411220546.352968</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>492.865</t>
+          <t>492865454.861185</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>525.058</t>
+          <t>525058362.089176</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1240.339</t>
+          <t>1240338748.29219</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1078.524</t>
+          <t>1078524349.3032</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1073.311</t>
+          <t>1073311443.20926</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1200.236</t>
+          <t>1200236432.97303</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1297.17</t>
+          <t>1297170393.13128</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1420.855</t>
+          <t>1420854773.73817</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1537.343</t>
+          <t>1537343458.76909</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1446.423</t>
+          <t>1446423084.03569</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1386.546</t>
+          <t>1386545505.38294</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1163.678</t>
+          <t>1163677574.19572</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1044.197</t>
+          <t>1044197414.97483</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>871.319</t>
+          <t>871319322.675844</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>629.859</t>
+          <t>629859080.152628</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>476.481</t>
+          <t>476480769.499866</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>484.89</t>
+          <t>484890467.904803</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>884.069</t>
+          <t>884068571.154658</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>825.489</t>
+          <t>825488547.307721</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>846.049</t>
+          <t>846048929.094722</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>948.708</t>
+          <t>948708112.833771</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1010.814</t>
+          <t>1010813943.06032</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1147.074</t>
+          <t>1147073968.04096</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1226.395</t>
+          <t>1226394567.46454</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1183.22</t>
+          <t>1183220083.07825</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1127.11</t>
+          <t>1127110438.72822</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>918.915</t>
+          <t>918915188.750253</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>807.946</t>
+          <t>807946127.76263</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>664.887</t>
+          <t>664887072.171172</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>497.019</t>
+          <t>497018973.548068</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>342.051</t>
+          <t>342051088.714273</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>339.758</t>
+          <t>339758194.657864</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>600.135</t>
+          <t>600135073.175992</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>577.569</t>
+          <t>577568525.030564</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>639.415</t>
+          <t>639415244.249118</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>741.729</t>
+          <t>741729079.671804</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>908.139</t>
+          <t>908139060.848565</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1008.95</t>
+          <t>1008949790.32184</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1057.607</t>
+          <t>1057607394.45519</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>968.643</t>
+          <t>968642544.891736</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>905.367</t>
+          <t>905367165.173959</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>764.737</t>
+          <t>764737019.57156</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>706.144</t>
+          <t>706144377.207181</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>603.173</t>
+          <t>603172936.966064</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>448.997</t>
+          <t>448997163.434485</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>320.248</t>
+          <t>320248046.34642</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>313.374</t>
+          <t>313373951.107708</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>875.488</t>
+          <t>875487562.442807</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>778.49</t>
+          <t>778489561.817796</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>790.783</t>
+          <t>790782818.595087</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>883.351</t>
+          <t>883351054.441829</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>972.695</t>
+          <t>972695483.807289</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1116.981</t>
+          <t>1116980805.46454</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1206.815</t>
+          <t>1206815264.50177</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1110.374</t>
+          <t>1110373919.17723</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1057.869</t>
+          <t>1057869270.67064</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>872.392</t>
+          <t>872392273.904385</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>797.522</t>
+          <t>797521890.468803</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>703.576</t>
+          <t>703576426.052189</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>511.901</t>
+          <t>511901335.707461</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>411.126</t>
+          <t>411126364.920653</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>383.494</t>
+          <t>383493923.348348</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>882.46</t>
+          <t>882459667.400999</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>773.591</t>
+          <t>773590511.994363</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>797.007</t>
+          <t>797006926.430894</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>910.419</t>
+          <t>910419168.400969</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1004.984</t>
+          <t>1004984144.32765</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1135.148</t>
+          <t>1135148115.04521</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1227.165</t>
+          <t>1227165386.69504</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1213.382</t>
+          <t>1213381651.13073</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1123.036</t>
+          <t>1123036148.14822</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>915.332</t>
+          <t>915332371.843994</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>796.861</t>
+          <t>796860724.707311</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>691.533</t>
+          <t>691532736.959332</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>520.375</t>
+          <t>520374718.915934</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>395.419</t>
+          <t>395418921.16291</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>394.052</t>
+          <t>394051591.208265</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>803.216</t>
+          <t>803216454.619827</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>728.129</t>
+          <t>728128630.641644</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>740.88</t>
+          <t>740879945.434698</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>811.566</t>
+          <t>811565922.437415</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>872.688</t>
+          <t>872687955.916447</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1008.282</t>
+          <t>1008281898.17397</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1072.027</t>
+          <t>1072026842.93598</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1049.71</t>
+          <t>1049710407.18017</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>993.966</t>
+          <t>993966357.685006</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>818.221</t>
+          <t>818221331.864372</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>727.225</t>
+          <t>727225087.357162</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>620.431</t>
+          <t>620430507.096749</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>456.061</t>
+          <t>456061292.654757</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>342.32</t>
+          <t>342319834.153307</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>330.422</t>
+          <t>330422254.324843</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>37535.634</t>
+          <t>37535633898.0291</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>33896.377</t>
+          <t>33896377400.4994</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>34986.894</t>
+          <t>34986893839.6443</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>39506.198</t>
+          <t>39506198462.4525</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>42605.691</t>
+          <t>42605691408.3103</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>47763.088</t>
+          <t>47763087740.3096</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>50764.954</t>
+          <t>50764953605.4454</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>48709.297</t>
+          <t>48709297242.2475</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>46037.613</t>
+          <t>46037612927.8368</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>37678.709</t>
+          <t>37678708642.2091</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>33712.888</t>
+          <t>33712887606.7158</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>28693.258</t>
+          <t>28693258172.0569</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>21313.005</t>
+          <t>21313005493.7667</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>16054.531</t>
+          <t>16054531040.7843</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>15984.764</t>
+          <t>15984764407.9258</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>value.m.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
